--- a/excel_templates/rnaseq_mirnaseq_manifest_template.xlsx
+++ b/excel_templates/rnaseq_mirnaseq_manifest_template.xlsx
@@ -1627,7 +1627,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>If fastq/bam files, are the reads paired end?</t>
+          <t>If FASTQ, BAM, or CRAM files, are the reads paired end?</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">

--- a/excel_templates/rnaseq_mirnaseq_manifest_template.xlsx
+++ b/excel_templates/rnaseq_mirnaseq_manifest_template.xlsx
@@ -1627,7 +1627,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>If fastq/bam files, are the reads paired end?</t>
+          <t>If FASTQ files, are the reads paired end?</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">

--- a/excel_templates/rnaseq_mirnaseq_manifest_template.xlsx
+++ b/excel_templates/rnaseq_mirnaseq_manifest_template.xlsx
@@ -1622,12 +1622,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>If FASTQ files, are the reads paired end?</t>
+          <t>If FASTQ files, are the reads paired end? Required when inputs are FASTQ files.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">

--- a/excel_templates/rnaseq_mirnaseq_manifest_template.xlsx
+++ b/excel_templates/rnaseq_mirnaseq_manifest_template.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>"Bone Marrow", "Buffy Coat", "Derived Cell Line", "Not Available", "Not Reported", "Patient Derived Xenograft", "Xenograft", "Patient Derived Organoid", "Peripheral Blood Mononuclear Cells", "Peripheral Whole Blood", "Saliva", "Solid Tissue", "Umbilical Cord Blood", "Patient-Derived T Cells", "Modified T Cells", "Patient-Derived Primary Cells", "iPSC-Derived Organoid", "Cerebrospinal Fluid", "Embryonic Stem Cell Derived Cell Line"</t>
+          <t>"Bone Marrow", "Buffy Coat", "Derived Cell Line", "Not Available", "Not Reported", "Patient Derived Xenograft", "Xenograft", "Patient Derived Organoid", "Peripheral Blood Mononuclear Cells", "Peripheral Whole Blood", "Saliva", "Solid Tissue", "Umbilical Cord Blood", "Patient-Derived T Cells", "Modified T Cells", "Patient-Derived Primary Cells", "iPSC-Derived Organoid", "Cerebrospinal Fluid", "Embryonic Stem Cell Derived Cell Line", "Extracellular Vesicles"</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -2394,7 +2394,7 @@
       <formula1>'Lists'!$B$2:$B$14</formula1>
     </dataValidation>
     <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$C$2:$C$20</formula1>
+      <formula1>'Lists'!$C$2:$C$21</formula1>
     </dataValidation>
     <dataValidation sqref="W2:W1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$D$2:$D$8</formula1>
@@ -3214,6 +3214,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Extracellular Vesicles</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>PED</t>

--- a/excel_templates/rnaseq_mirnaseq_manifest_template.xlsx
+++ b/excel_templates/rnaseq_mirnaseq_manifest_template.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$G$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$G$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -772,7 +772,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>"Bone Marrow", "Buffy Coat", "Derived Cell Line", "Not Available", "Not Reported", "Patient Derived Xenograft", "Xenograft", "Patient Derived Organoid", "Peripheral Blood Mononuclear Cells", "Peripheral Whole Blood", "Saliva", "Solid Tissue", "Umbilical Cord Blood", "Patient-Derived T Cells", "Modified T Cells", "Patient-Derived Primary Cells", "iPSC-Derived Organoid", "Cerebrospinal Fluid", "Embryonic Stem Cell Derived Cell Line", "Extracellular Vesicles"</t>
+          <t>"Bone Marrow", "Buffy Coat", "Derived Cell Line", "Not Available", "Not Reported", "Patient Derived Xenograft", "Xenograft", "Patient Derived Organoid", "Peripheral Blood Mononuclear Cells", "Peripheral Whole Blood", "Saliva", "Solid Tissue", "Umbilical Cord Blood", "Patient-Derived T Cells", "Modified T Cells", "Patient-Derived Primary Cells", "iPSC-Derived Organoid", "Cerebrospinal Fluid", "Embryonic Stem Cell Derived Cell Line"</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -790,7 +790,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>bio_replicate</t>
+          <t>sample_fraction</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -800,10 +800,14 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Label identifying the biological replicate this sample represents</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr"/>
+          <t>Fraction isolated from the sample source recorded in composition (e.g. extracellular vesicles from primary NK cells); leave blank for whole-sample material</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>"Large Extracellular Vesicles", "Small Extracellular Vesicles"</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -811,7 +815,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Rep1</t>
+          <t>Small Extracellular Vesicles</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -819,7 +823,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>dose_1</t>
+          <t>bio_replicate</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -829,7 +833,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Dose for treatment_1 in a simultaneous combination treatment</t>
+          <t>Label identifying the biological replicate this sample represents</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr"/>
@@ -840,7 +844,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10 nM</t>
+          <t>Rep1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -848,7 +852,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>dose_2</t>
+          <t>dose_1</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -858,7 +862,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Dose for treatment_2 in a simultaneous combination treatment</t>
+          <t>Dose for treatment_1 in a simultaneous combination treatment</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr"/>
@@ -869,7 +873,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20 nM</t>
+          <t>10 nM</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -877,7 +881,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>treatment_1</t>
+          <t>dose_2</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -887,7 +891,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>First component of a simultaneous combination treatment administered or applied to the sample</t>
+          <t>Dose for treatment_2 in a simultaneous combination treatment</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr"/>
@@ -898,7 +902,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>temozolomide</t>
+          <t>20 nM</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
@@ -906,7 +910,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>treatment_2</t>
+          <t>treatment_1</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -916,7 +920,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Second component of a simultaneous combination treatment administered or applied to the sample</t>
+          <t>First component of a simultaneous combination treatment administered or applied to the sample</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr"/>
@@ -927,7 +931,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>radiation</t>
+          <t>temozolomide</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -935,7 +939,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>cell_line_composition</t>
+          <t>treatment_2</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -945,7 +949,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Culture media used for the cell line, for a "Derived Cell Line" composition</t>
+          <t>Second component of a simultaneous combination treatment administered or applied to the sample</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr"/>
@@ -956,7 +960,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>DMEM/F12</t>
+          <t>radiation</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
@@ -964,7 +968,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>cell_line_passage</t>
+          <t>cell_line_composition</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -974,18 +978,18 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Numeric passage number for the cell line, for a "Derived Cell Line" composition</t>
+          <t>Culture media used for the cell line, for a "Derived Cell Line" composition</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>DMEM/F12</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -993,7 +997,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>timepoint</t>
+          <t>cell_line_passage</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1003,18 +1007,18 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Timepoint associated with the treatment, collection, or experiment</t>
+          <t>Numeric passage number for the cell line, for a "Derived Cell Line" composition</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24h</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
@@ -1022,7 +1026,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>parental_model_id</t>
+          <t>timepoint</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1032,7 +1036,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Identifier for the parental model. Required for model-derived samples, including cell lines, xenografts, organoids, and other derived cell-line models; use this value for participant_id for model submissions</t>
+          <t>Timepoint associated with the treatment, collection, or experiment</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr"/>
@@ -1043,7 +1047,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>CNMC-XD760</t>
+          <t>24h</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -1051,7 +1055,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>model_id</t>
+          <t>parental_model_id</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1061,7 +1065,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Identifier for the submitted model, including genetically modified cell lines or other model derivatives. Required for model-derived samples, including cell lines, xenografts, organoids, and other derived cell-line models</t>
+          <t>Identifier for the parental model. Required for model-derived samples, including cell lines, xenografts, organoids, and other derived cell-line models; use this value for participant_id for model submissions</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr"/>
@@ -1072,7 +1076,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>CNMC-XD760-mCherry-Luciferase</t>
+          <t>CNMC-XD760</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
@@ -1080,7 +1084,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>local_dir_path</t>
+          <t>model_id</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1090,7 +1094,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>SMB directory path on the L Drive for the source data. Required when file_source_platform is local_drive or bti_aws_and_local_drive</t>
+          <t>Identifier for the submitted model, including genetically modified cell lines or other model derivatives. Required for model-derived samples, including cell lines, xenografts, organoids, and other derived cell-line models</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
@@ -1101,7 +1105,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>smb://cnmc.org/cri/Lab/CancerImmunology-BTI</t>
+          <t>CNMC-XD760-mCherry-Luciferase</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
@@ -1109,7 +1113,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>aws_s3_path</t>
+          <t>local_dir_path</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1119,7 +1123,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>S3 URI for the submitted data location. Required when file_source_platform is bti_aws or bti_aws_and_local_drive</t>
+          <t>SMB directory path on the L Drive for the source data. Required when file_source_platform is local_drive or bti_aws_and_local_drive</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr"/>
@@ -1130,7 +1134,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>s3://bucket/prefix</t>
+          <t>smb://cnmc.org/cri/Lab/CancerImmunology-BTI</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
@@ -1138,24 +1142,20 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>file_source_platform</t>
+          <t>aws_s3_path</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Source platform where files are stored and from which they are harmonized</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>"bti_aws", "local_drive", "bti_aws_and_local_drive", "cgc", "kids_first", "sra", "synapse"</t>
-        </is>
-      </c>
+          <t>S3 URI for the submitted data location. Required when file_source_platform is bti_aws or bti_aws_and_local_drive</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>bti_aws</t>
+          <t>s3://bucket/prefix</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -1171,20 +1171,24 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>sequencing_batch</t>
+          <t>file_source_platform</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Sequencing batch identifier</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr"/>
+          <t>Source platform where files are stored and from which they are harmonized</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>"bti_aws", "local_drive", "bti_aws_and_local_drive", "cgc", "kids_first", "sra", "synapse"</t>
+        </is>
+      </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1192,7 +1196,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>30-XXXXXXXX</t>
+          <t>bti_aws</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
@@ -1200,17 +1204,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>file_name</t>
+          <t>sequencing_batch</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Name of the file</t>
+          <t>Sequencing batch identifier</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
@@ -1221,7 +1225,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>NCI-11Plex-13-F12A-z11358.fastq</t>
+          <t>30-XXXXXXXX</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -1229,7 +1233,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>file_format</t>
+          <t>file_name</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1239,14 +1243,10 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Format of the file</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>"FASTQ", "BAM", "BAI", "CRAM", "CRAI", "GVCF", "VCF", "TBI", "MAF", "PDF", "HTML", "DCM", "IDAT", "SVS", "GPR", "CNS", "TXT", "PNG", "CSV", "PED", "SEG", "TAR", "TSV", "mzML", "raw"</t>
-        </is>
-      </c>
+          <t>Name of the file</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>FASTQ</t>
+          <t>NCI-11Plex-13-F12A-z11358.fastq</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
@@ -1262,7 +1262,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>file_size</t>
+          <t>file_format</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1272,18 +1272,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Reported file size in bytes</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr"/>
+          <t>Format of the file</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>"FASTQ", "BAM", "BAI", "CRAM", "CRAI", "GVCF", "VCF", "TBI", "MAF", "PDF", "HTML", "DCM", "IDAT", "SVS", "GPR", "CNS", "TXT", "PNG", "CSV", "PED", "SEG", "TAR", "TSV", "mzML", "raw"</t>
+        </is>
+      </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>529600</t>
+          <t>FASTQ</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -1291,7 +1295,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>file_hash_type</t>
+          <t>file_size</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1301,30 +1305,26 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Hash algorithm used to generate file hash</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>"MD5", "SHA1", "SHA256", "SHA512", "ETag"</t>
-        </is>
-      </c>
+          <t>Reported file size in bytes</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>MD5</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="n"/>
+          <t>529600</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>file_hash_value</t>
+          <t>file_hash_type</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1334,10 +1334,14 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Full has value of the file</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr"/>
+          <t>Hash algorithm used to generate file hash</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>"MD5", "SHA1", "SHA256", "SHA512", "ETag"</t>
+        </is>
+      </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1345,25 +1349,25 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>938c2cc0dcc05f2b68c4287040cfcf71</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr"/>
+          <t>MD5</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>sequencing_center</t>
+          <t>file_hash_value</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Name of the center generating sequencing data</t>
+          <t>Full has value of the file</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr"/>
@@ -1374,7 +1378,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Harvard Med School</t>
+          <t>938c2cc0dcc05f2b68c4287040cfcf71</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
@@ -1382,24 +1386,20 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>instrument_platform</t>
+          <t>sequencing_center</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Name of the platform used to obtain data</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>"Complete Genomics", "Illumina", "Ion Torrent", "LS454", "SOLiD", "ONT", "DNBSEQ", "PacBio SMRT Cell", "Other"</t>
-        </is>
-      </c>
+          <t>Name of the center generating sequencing data</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Illumina</t>
+          <t>Harvard Med School</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
@@ -1415,32 +1415,32 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>instrument_model</t>
+          <t>instrument_platform</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Specific model of sequencing instrument used.</t>
+          <t>Name of the platform used to obtain data</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>"Complete Genomics", "Illumina", "Ion Torrent", "LS454", "SOLiD", "ONT", "DNBSEQ", "PacBio SMRT Cell", "Other"</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Model name of the instrument used for sequencing</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>NovaSeq 6000</t>
+          <t>Illumina</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
@@ -1448,32 +1448,32 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>experimental_strategy</t>
+          <t>instrument_model</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>The sequencing strategy used to generate the data file.</t>
+          <t>Specific model of sequencing instrument used.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>"RNA-Seq","miRNA-Seq", "Ribo-Seq", "long-read RNA-Seq", "Flash-Seq"</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>Model name of the instrument used for sequencing</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>RNA-Seq</t>
+          <t>NovaSeq 6000</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
@@ -1481,7 +1481,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>library_selection</t>
+          <t>experimental_strategy</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Library selection method. "Random Fragmentation" indicates libraries generated by shearing or chemical fragmentation (e.g., alkaline hydrolysis) rather than a targeted enrichment/selection step.</t>
+          <t>The sequencing strategy used to generate the data file.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>"Affinity Enrichment", "Hybrid Selection", "miRNA Size Fractionation", "PCR", "Poly-T Enrichment", "Random Fragmentation","rRNA Depletion", "Ribosome-protected fragments", "Other"</t>
+          <t>"RNA-Seq","miRNA-Seq", "Ribo-Seq", "long-read RNA-Seq", "Flash-Seq"</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Poly-T Enrichment</t>
+          <t>RNA-Seq</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
@@ -1514,7 +1514,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>library_strand</t>
+          <t>library_selection</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1524,12 +1524,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Library strandedness.</t>
+          <t>Library selection method. "Random Fragmentation" indicates libraries generated by shearing or chemical fragmentation (e.g., alkaline hydrolysis) rather than a targeted enrichment/selection step.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>"Stranded", "Unstranded", "First Stranded", "Second Stranded", "Unknown"</t>
+          <t>"Affinity Enrichment", "Hybrid Selection", "miRNA Size Fractionation", "PCR", "Poly-T Enrichment", "Random Fragmentation","rRNA Depletion", "Ribosome-protected fragments", "Other"</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Stranded</t>
+          <t>Poly-T Enrichment</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
@@ -1547,7 +1547,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>library_prep</t>
+          <t>library_strand</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Library prep method.</t>
+          <t>Library strandedness.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>"polyA", "totalRNAseq", "Other"</t>
+          <t>"Stranded", "Unstranded", "First Stranded", "Second Stranded", "Unknown"</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>polyA</t>
+          <t>Stranded</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
@@ -1580,7 +1580,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>RNA_library</t>
+          <t>library_prep</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1590,12 +1590,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Library category. For miRNA-Seq, use "small RNA first-stranded". For unstranded polyA libraries, use "poly-A unstranded". For Random Fragmentation libraries, use "fragmented".</t>
+          <t>Library prep method.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>"exome capture", "fragmented", "poly-A", "poly-A stranded", "poly-A unstranded", "RPFs", "total RNA stranded", "total RNA unstranded", "small RNA first-stranded"</t>
+          <t>"polyA", "totalRNAseq", "Other"</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1605,52 +1605,52 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>total RNA stranded</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+          <t>polyA</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>is_paired_end</t>
+          <t>RNA_library</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>If FASTQ files, are the reads paired end? Required when inputs are FASTQ files.</t>
+          <t>Library category. For miRNA-Seq, use "small RNA first-stranded". For unstranded polyA libraries, use "poly-A unstranded". For Random Fragmentation libraries, use "fragmented".</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>"True", "False"</t>
+          <t>"exome capture", "fragmented", "poly-A", "poly-A stranded", "poly-A unstranded", "RPFs", "total RNA stranded", "total RNA unstranded", "small RNA first-stranded"</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
+          <t>total RNA stranded</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>read_pair_number</t>
+          <t>is_paired_end</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Denotes whether a submitted FASTQ file contains forward (R1) or reverse (R2) reads for paired-end sequencing. Required when inputs are FASTQ files.</t>
+          <t>If FASTQ files, are the reads paired end? Required when inputs are FASTQ files.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>"R1", "R2", "NA"</t>
+          <t>"True", "False"</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>True</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
@@ -1683,7 +1683,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>flow_cell_barcode</t>
+          <t>read_pair_number</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -1693,10 +1693,14 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Flow cell barcode. Wrong or missing information may affect analysis results. Required when inputs are FASTQ files.</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr"/>
+          <t>Denotes whether a submitted FASTQ file contains forward (R1) or reverse (R2) reads for paired-end sequencing. Required when inputs are FASTQ files.</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>"R1", "R2", "NA"</t>
+        </is>
+      </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1704,7 +1708,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>H0164ALXX140820</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
@@ -1712,7 +1716,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>lane_number</t>
+          <t>flow_cell_barcode</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1722,7 +1726,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>The basic machine unit for sequencing. For Illumina machines, this reflects the physical lane number. Wrong or missing information may affect analysis results. Required when inputs are FASTQ files.</t>
+          <t>Flow cell barcode. Wrong or missing information may affect analysis results. Required when inputs are FASTQ files.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
@@ -1733,7 +1737,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>H0164ALXX140820</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
@@ -1741,7 +1745,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>is_adapter_trimmed</t>
+          <t>lane_number</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -1751,22 +1755,18 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Were adapters trimmed from sequencing data? Not required, as adapter presence is detected downstream; fill in if known. Only applies to FASTQ files.</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>"True", "False", "Unknown"</t>
-        </is>
-      </c>
+          <t>The basic machine unit for sequencing. For Illumina machines, this reflects the physical lane number. Wrong or missing information may affect analysis results. Required when inputs are FASTQ files.</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr"/>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>boolean/string</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
@@ -1774,7 +1774,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>adapter_sequencing</t>
+          <t>is_adapter_trimmed</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1784,18 +1784,22 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Base sequence of the sequencing adapter. Only applies when adapters were not trimmed.</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr"/>
+          <t>Were adapters trimmed from sequencing data? Not required, as adapter presence is detected downstream; fill in if known. Only applies to FASTQ files.</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>"True", "False", "Unknown"</t>
+        </is>
+      </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean/string</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>AGATCGGAAGAGCGTCGTGTAGGGAAAGAGTGT</t>
+          <t>False</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
@@ -1803,7 +1807,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>total_reads</t>
+          <t>adapter_sequencing</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -1813,18 +1817,18 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Total number of reads that align to the reference.</t>
+          <t>Base sequence of the sequencing adapter. Only applies when adapters were not trimmed.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>525600</t>
+          <t>AGATCGGAAGAGCGTCGTGTAGGGAAAGAGTGT</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
@@ -1832,7 +1836,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>reference_genome</t>
+          <t>total_reads</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1842,18 +1846,18 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Reference genome version. Required when file_format is "BAM" or "CRAM"</t>
+          <t>Total number of reads that align to the reference.</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>GRCH38</t>
+          <t>525600</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
@@ -1861,32 +1865,28 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>FFPE</t>
+          <t>reference_genome</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Is the sample preserved in FFPE</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>"True", "False"</t>
-        </is>
-      </c>
+          <t>Reference genome version. Required when file_format is "BAM" or "CRAM"</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr"/>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>GRCH38</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
@@ -1894,7 +1894,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>PI_name</t>
+          <t>FFPE</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -1904,30 +1904,30 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Principal Investigator of the project</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr"/>
+          <t>Is the sample preserved in FFPE</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>"True", "False"</t>
+        </is>
+      </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Fonseca</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>project</t>
+          <t>PI_name</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Short name of the project</t>
+          <t>Principal Investigator of the project</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>RBT</t>
+          <t>Fonseca</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>organism</t>
+          <t>project</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -1970,14 +1970,10 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Binomial name of organism with full genus name</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>"Homo sapiens", "Mus musculus"</t>
-        </is>
-      </c>
+          <t>Short name of the project</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr"/>
       <c r="E50" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1985,30 +1981,34 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Homo sapiens</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr"/>
+          <t>RBT</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>host_organism</t>
+          <t>organism</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Host organism binomial name when the sequenced sample is a xenograft. Required when compisition is "Patient Derived Xenograft" or "Xenograft"</t>
+          <t>Binomial name of organism with full genus name</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>"Mus musculus"</t>
+          <t>"Homo sapiens", "Mus musculus"</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2018,50 +2018,83 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Mus musculus</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>host_organism</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Host organism binomial name when the sequenced sample is a xenograft. Required when compisition is "Patient Derived Xenograft" or "Xenograft"</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>"Mus musculus"</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Mus musculus</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
           <t>reported_gender</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>Reported gender of the participant. Required when organism is "Homo sapiens"</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>"Female", "Male", "Not Reported"</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G52"/>
+  <autoFilter ref="A1:G53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2072,7 +2105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY1"/>
+  <dimension ref="A1:AZ1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2126,6 +2159,7 @@
     <col width="24" customWidth="1" min="49" max="49"/>
     <col width="24" customWidth="1" min="50" max="50"/>
     <col width="24" customWidth="1" min="51" max="51"/>
+    <col width="24" customWidth="1" min="52" max="52"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2181,212 +2215,217 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>sample_fraction</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>bio_replicate</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>dose_1</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>dose_2</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>treatment_1</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>treatment_2</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>cell_line_composition</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>cell_line_passage</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>timepoint</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>parental_model_id</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>model_id</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>local_dir_path</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>aws_s3_path</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>file_source_platform</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>sequencing_batch</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>file_name</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>file_format</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>file_size</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>file_hash_type</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>file_hash_value</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>sequencing_center</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>instrument_platform</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>instrument_model</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>experimental_strategy</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>library_selection</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>library_strand</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>library_prep</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>RNA_library</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>is_paired_end</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>read_pair_number</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>flow_cell_barcode</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>lane_number</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>is_adapter_trimmed</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>adapter_sequencing</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>total_reads</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>reference_genome</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>FFPE</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>PI_name</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>project</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>organism</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>host_organism</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>reported_gender</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="19">
+  <dataValidations count="20">
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$A$2:$A$6</formula1>
     </dataValidation>
@@ -2394,55 +2433,58 @@
       <formula1>'Lists'!$B$2:$B$14</formula1>
     </dataValidation>
     <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$C$2:$C$21</formula1>
+      <formula1>'Lists'!$C$2:$C$20</formula1>
     </dataValidation>
-    <dataValidation sqref="W2:W1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$D$2:$D$8</formula1>
+    <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$D$2:$D$3</formula1>
     </dataValidation>
-    <dataValidation sqref="Z2:Z1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$E$2:$E$26</formula1>
+    <dataValidation sqref="X2:X1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$E$2:$E$8</formula1>
     </dataValidation>
-    <dataValidation sqref="AB2:AB1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$F$2:$F$6</formula1>
+    <dataValidation sqref="AA2:AA1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$F$2:$F$26</formula1>
     </dataValidation>
-    <dataValidation sqref="AE2:AE1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$G$2:$G$10</formula1>
+    <dataValidation sqref="AC2:AC1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$G$2:$G$6</formula1>
     </dataValidation>
-    <dataValidation sqref="AG2:AG1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$H$2:$H$6</formula1>
+    <dataValidation sqref="AF2:AF1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$H$2:$H$10</formula1>
     </dataValidation>
     <dataValidation sqref="AH2:AH1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$I$2:$I$10</formula1>
+      <formula1>'Lists'!$I$2:$I$6</formula1>
     </dataValidation>
     <dataValidation sqref="AI2:AI1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$J$2:$J$6</formula1>
+      <formula1>'Lists'!$J$2:$J$10</formula1>
     </dataValidation>
     <dataValidation sqref="AJ2:AJ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$K$2:$K$4</formula1>
+      <formula1>'Lists'!$K$2:$K$6</formula1>
     </dataValidation>
     <dataValidation sqref="AK2:AK1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$L$2:$L$10</formula1>
+      <formula1>'Lists'!$L$2:$L$4</formula1>
     </dataValidation>
     <dataValidation sqref="AL2:AL1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$M$2:$M$3</formula1>
+      <formula1>'Lists'!$M$2:$M$10</formula1>
     </dataValidation>
     <dataValidation sqref="AM2:AM1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$N$2:$N$4</formula1>
+      <formula1>'Lists'!$N$2:$N$3</formula1>
     </dataValidation>
-    <dataValidation sqref="AP2:AP1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AN2:AN1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$O$2:$O$4</formula1>
     </dataValidation>
-    <dataValidation sqref="AT2:AT1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$P$2:$P$3</formula1>
+    <dataValidation sqref="AQ2:AQ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$P$2:$P$4</formula1>
     </dataValidation>
-    <dataValidation sqref="AW2:AW1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AU2:AU1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$Q$2:$Q$3</formula1>
     </dataValidation>
     <dataValidation sqref="AX2:AX1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$R$2:$R$2</formula1>
+      <formula1>'Lists'!$R$2:$R$3</formula1>
     </dataValidation>
     <dataValidation sqref="AY2:AY1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$S$2:$S$4</formula1>
+      <formula1>'Lists'!$S$2:$S$2</formula1>
+    </dataValidation>
+    <dataValidation sqref="AZ2:AZ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$T$2:$T$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2455,7 +2497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:T26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2476,80 +2518,85 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>sample_fraction</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>file_source_platform</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>file_format</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>file_hash_type</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>instrument_platform</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>experimental_strategy</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>library_selection</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>library_strand</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>library_prep</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>RNA_library</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>is_paired_end</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>read_pair_number</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>is_adapter_trimmed</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>FFPE</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>organism</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>host_organism</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>reported_gender</t>
         </is>
@@ -2573,80 +2620,85 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Large Extracellular Vesicles</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>bti_aws</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>FASTQ</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>MD5</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Complete Genomics</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>RNA-Seq</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Affinity Enrichment</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Stranded</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>polyA</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>exome capture</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Mus musculus</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
@@ -2670,64 +2722,64 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Small Extracellular Vesicles</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>local_drive</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>BAM</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>SHA1</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Illumina</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>miRNA-Seq</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Hybrid Selection</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Unstranded</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>totalRNAseq</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>fragmented</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>False</t>
@@ -2735,10 +2787,15 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>Mus musculus</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2760,62 +2817,62 @@
           <t>Derived Cell Line</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>bti_aws_and_local_drive</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>BAI</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>SHA256</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Ion Torrent</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Ribo-Seq</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>miRNA Size Fractionation</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>First Stranded</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>poly-A</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Not Reported</t>
         </is>
@@ -2837,42 +2894,42 @@
           <t>Not Available</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>cgc</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>CRAM</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>SHA512</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>LS454</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>long-read RNA-Seq</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>PCR</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Second Stranded</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>poly-A stranded</t>
         </is>
@@ -2894,42 +2951,42 @@
           <t>Not Reported</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>kids_first</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>CRAI</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>ETag</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>SOLiD</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Flash-Seq</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Poly-T Enrichment</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>poly-A unstranded</t>
         </is>
@@ -2946,27 +3003,27 @@
           <t>Patient Derived Xenograft</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>sra</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>GVCF</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>ONT</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Random Fragmentation</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>RPFs</t>
         </is>
@@ -2983,27 +3040,27 @@
           <t>Xenograft</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>synapse</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>VCF</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>DNBSEQ</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>rRNA Depletion</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>total RNA stranded</t>
         </is>
@@ -3020,22 +3077,22 @@
           <t>Patient Derived Organoid</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>TBI</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>PacBio SMRT Cell</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Ribosome-protected fragments</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>total RNA unstranded</t>
         </is>
@@ -3052,22 +3109,22 @@
           <t>Peripheral Blood Mononuclear Cells</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>MAF</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>small RNA first-stranded</t>
         </is>
@@ -3084,7 +3141,7 @@
           <t>Peripheral Whole Blood</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -3101,7 +3158,7 @@
           <t>Saliva</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
@@ -3118,7 +3175,7 @@
           <t>Solid Tissue</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>DCM</t>
         </is>
@@ -3135,7 +3192,7 @@
           <t>Umbilical Cord Blood</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>IDAT</t>
         </is>
@@ -3147,7 +3204,7 @@
           <t>Patient-Derived T Cells</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>SVS</t>
         </is>
@@ -3159,7 +3216,7 @@
           <t>Modified T Cells</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>GPR</t>
         </is>
@@ -3171,7 +3228,7 @@
           <t>Patient-Derived Primary Cells</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>CNS</t>
         </is>
@@ -3183,7 +3240,7 @@
           <t>iPSC-Derived Organoid</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>TXT</t>
         </is>
@@ -3195,7 +3252,7 @@
           <t>Cerebrospinal Fluid</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>PNG</t>
         </is>
@@ -3207,54 +3264,49 @@
           <t>Embryonic Stem Cell Derived Cell Line</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>CSV</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Extracellular Vesicles</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>PED</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>SEG</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>TAR</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>TSV</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>mzML</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
